--- a/algandmed/Andmesõnastik.xlsx
+++ b/algandmed/Andmesõnastik.xlsx
@@ -8,20 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opilane\Documents\Koolituste-kasumlikkuse-m-jutegurid\algandmed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3123F0-0188-4042-8E28-6F447FAE0F42}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5FD38BE-21F2-4D2A-97FC-4A9326288AAF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25065" windowHeight="8970" activeTab="7" xr2:uid="{FBB6913D-FBE4-4976-8EF8-9C17E1C42A8C}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25065" windowHeight="8970" tabRatio="859" firstSheet="5" activeTab="9" xr2:uid="{FBB6913D-FBE4-4976-8EF8-9C17E1C42A8C}"/>
   </bookViews>
   <sheets>
-    <sheet name="EA" sheetId="1" r:id="rId1"/>
-    <sheet name="EAT" sheetId="2" r:id="rId2"/>
-    <sheet name="koolitused" sheetId="3" r:id="rId3"/>
-    <sheet name="kulud või tulud" sheetId="4" r:id="rId4"/>
-    <sheet name="Töö ja koolitustunnid" sheetId="5" r:id="rId5"/>
+    <sheet name="EA" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="EAT" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="koolitused" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="kulud või tulud" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="Töö ja koolitustunnid" sheetId="5" state="hidden" r:id="rId5"/>
     <sheet name="Ärisõnastik" sheetId="6" r:id="rId6"/>
     <sheet name="Andmesõnastik (ek)" sheetId="7" r:id="rId7"/>
     <sheet name="Andmesõnastik (ingl)" sheetId="8" r:id="rId8"/>
+    <sheet name="hüpoteesid" sheetId="9" r:id="rId9"/>
+    <sheet name="projektid" sheetId="11" r:id="rId10"/>
+    <sheet name="dashboard soovitus ai" sheetId="10" r:id="rId11"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Andmesõnastik (ingl)'!$A$1:$F$51</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -32,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="289">
   <si>
     <t>KontoNr</t>
   </si>
@@ -236,9 +242,6 @@
   </si>
   <si>
     <t>millised koolitused on kahjumlikud ja mille tõttu? Ettepanekud</t>
-  </si>
-  <si>
-    <t>osalejate arv, koolituse pikkus, kategooria kuidas mõjutab kasumlikkust?</t>
   </si>
   <si>
     <t xml:space="preserve"> Koolitus, kuhu saavad tulla erinevate ettevõtete töötajad või eraisikud (Seotud andmetes:  avalik või sise märkega "Avalik", Käive_avalik).</t>
@@ -593,42 +596,6 @@
     <t>Indicates whether the transaction belongs to a public course or internal B2B.</t>
   </si>
   <si>
-    <t>Account Number</t>
-  </si>
-  <si>
-    <t>Budget Date</t>
-  </si>
-  <si>
-    <t>Budget Amount</t>
-  </si>
-  <si>
-    <t>Cost Center</t>
-  </si>
-  <si>
-    <t>Project Code</t>
-  </si>
-  <si>
-    <t>Financial Mapping Key</t>
-  </si>
-  <si>
-    <t>Actual Date</t>
-  </si>
-  <si>
-    <t>Actual Amount</t>
-  </si>
-  <si>
-    <t>Transaction Type</t>
-  </si>
-  <si>
-    <t>Document Number</t>
-  </si>
-  <si>
-    <t>Invoice Number</t>
-  </si>
-  <si>
-    <t>Course Format</t>
-  </si>
-  <si>
     <t>Training Unique Name</t>
   </si>
   <si>
@@ -684,13 +651,268 @@
   </si>
   <si>
     <t>The exact date the actual financial transaction occurred (DD.MM.YYYY).</t>
+  </si>
+  <si>
+    <t>kas tulu on koolituse alguse v lõpukpv kuus</t>
+  </si>
+  <si>
+    <t>osalejate arv, koolituse pikkus, koolitaja ja  kategooria - kuidas mõjutab kasumlikkust?</t>
+  </si>
+  <si>
+    <t>Column name in English</t>
+  </si>
+  <si>
+    <t>mida see nr näitab?</t>
+  </si>
+  <si>
+    <t>miks korrutis osalejate arvuga ei võrdu käibega?</t>
+  </si>
+  <si>
+    <t>eraldame end_date (hooajalisus!)</t>
+  </si>
+  <si>
+    <t>kuidas täiskomplekt ridu kuvada?</t>
+  </si>
+  <si>
+    <t>koolituse tulud saame koolituste tabelist (käive kokku) ja koolitusega seotud kulud proovime tuletada EAT tabelist (selle koolituse proportsioon kogukuludest (mille alusel?))</t>
+  </si>
+  <si>
+    <t>2. Osalejate arvu mõju kasumile</t>
+  </si>
+  <si>
+    <t>1. Kasum koolituse kohta</t>
+  </si>
+  <si>
+    <t>tulu osaleja kohta, kulu osaleja kohta</t>
+  </si>
+  <si>
+    <t>X = osalejate arv</t>
+  </si>
+  <si>
+    <t>Y = kasum %</t>
+  </si>
+  <si>
+    <t>Size = käive</t>
+  </si>
+  <si>
+    <t>💡 Insight:</t>
+  </si>
+  <si>
+    <t>kas väiksed grupid on kahjumlikud?</t>
+  </si>
+  <si>
+    <t>kus on “break-even” osalejate arv?</t>
+  </si>
+  <si>
+    <t>Scatter plot:</t>
+  </si>
+  <si>
+    <t>3. Kas tegelik hind optimaalne?</t>
+  </si>
+  <si>
+    <t>arvutame osaleja tegeliku hinna e/v jaoks välja (käive kokku alusel)</t>
+  </si>
+  <si>
+    <t>Segment:</t>
+  </si>
+  <si>
+    <t>koolitus</t>
+  </si>
+  <si>
+    <t>kategooria</t>
+  </si>
+  <si>
+    <t>👉 Visual:</t>
+  </si>
+  <si>
+    <t>Boxplot / avg price per category</t>
+  </si>
+  <si>
+    <t>vs kasum %</t>
+  </si>
+  <si>
+    <t>sama kategooria koolitused → erinev hind → erinev kasum</t>
+  </si>
+  <si>
+    <t>võimalus:</t>
+  </si>
+  <si>
+    <t>tõsta hinda</t>
+  </si>
+  <si>
+    <t>standardiseerida hinnastamine</t>
+  </si>
+  <si>
+    <t>4. Koolitajate kasumlikkus</t>
+  </si>
+  <si>
+    <t>kas on võimalik v mitte?</t>
+  </si>
+  <si>
+    <t>5. B2B vs avalik koolitus</t>
+  </si>
+  <si>
+    <t>Sul on:</t>
+  </si>
+  <si>
+    <t>👉 Võrdle:</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Public</t>
+  </si>
+  <si>
+    <t>B2B</t>
+  </si>
+  <si>
+    <t>Avg kasum %</t>
+  </si>
+  <si>
+    <t>Avg osalejad</t>
+  </si>
+  <si>
+    <t>Revenue per training</t>
+  </si>
+  <si>
+    <t>sageli:</t>
+  </si>
+  <si>
+    <t>B2B = suurem käive, väiksem marginaal</t>
+  </si>
+  <si>
+    <t>Public = väiksem käive, suurem marginaal</t>
+  </si>
+  <si>
+    <t>👉 otsus:</t>
+  </si>
+  <si>
+    <t>kuhu rohkem müüki suunata?</t>
+  </si>
+  <si>
+    <t>6. Aja trendid (hooajalisus)</t>
+  </si>
+  <si>
+    <t>Month vs:</t>
+  </si>
+  <si>
+    <t>käive</t>
+  </si>
+  <si>
+    <t>kasum</t>
+  </si>
+  <si>
+    <t>osalejad</t>
+  </si>
+  <si>
+    <t>hooajalisus</t>
+  </si>
+  <si>
+    <t>millal:</t>
+  </si>
+  <si>
+    <t>hinnatõus</t>
+  </si>
+  <si>
+    <t>kampaaniad</t>
+  </si>
+  <si>
+    <t>7. Kobarkoolitus vs tavaline</t>
+  </si>
+  <si>
+    <t>kasum %</t>
+  </si>
+  <si>
+    <t>kas kobarkoolitus tasub ära?</t>
+  </si>
+  <si>
+    <t>Pane kokku 1 leht:</t>
+  </si>
+  <si>
+    <t>TOP KPI-d</t>
+  </si>
+  <si>
+    <t>Käive</t>
+  </si>
+  <si>
+    <t>Kasum</t>
+  </si>
+  <si>
+    <t>Kasum %</t>
+  </si>
+  <si>
+    <t>Visualid</t>
+  </si>
+  <si>
+    <t>Kasum koolituse lõikes (bar)</t>
+  </si>
+  <si>
+    <t>Kasum % vs osalejad (scatter)</t>
+  </si>
+  <si>
+    <t>Trainer performance</t>
+  </si>
+  <si>
+    <t>Public vs B2B (stacked bar)</t>
+  </si>
+  <si>
+    <t>Aja trend (line)</t>
+  </si>
+  <si>
+    <t>Power BI dashboard</t>
+  </si>
+  <si>
+    <t>AZZ</t>
+  </si>
+  <si>
+    <t>üldkulud, üldtulud</t>
+  </si>
+  <si>
+    <t>PRO</t>
+  </si>
+  <si>
+    <t>projektid</t>
+  </si>
+  <si>
+    <t>KAS</t>
+  </si>
+  <si>
+    <t>kasutajatele suunatud koolitus</t>
+  </si>
+  <si>
+    <t>DEV</t>
+  </si>
+  <si>
+    <t>juhtidele suunatud koolitus</t>
+  </si>
+  <si>
+    <t>SKBY</t>
+  </si>
+  <si>
+    <t>õpidisain, keegi ei koolita, vaid on tehniline töö</t>
+  </si>
+  <si>
+    <t>SPE</t>
+  </si>
+  <si>
+    <t>spetsialistidele suunatud koolitus</t>
+  </si>
+  <si>
+    <t>GRF</t>
+  </si>
+  <si>
+    <t>SKB</t>
+  </si>
+  <si>
+    <t>tuleks koos KAS-iga  vaadata</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -784,8 +1006,77 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="186"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="186"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -798,8 +1089,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -822,12 +1125,79 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFDDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
@@ -855,6 +1225,56 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1215,6 +1635,167 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B90F5CF4-EA12-4035-9F90-A5B596104000}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="44.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" thickBot="1">
+      <c r="A2" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="32" t="s">
+        <v>278</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="33" t="s">
+        <v>280</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="33" t="s">
+        <v>282</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.75" thickBot="1">
+      <c r="A6" s="34" t="s">
+        <v>284</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="35" t="s">
+        <v>286</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="35" t="s">
+        <v>287</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>288</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F74DF8-85C5-4C33-AFA1-2DA6DBD191B2}">
+  <dimension ref="A1:A18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="35.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="31.5">
+      <c r="A1" s="26" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="18">
+      <c r="A5" s="27" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="21"/>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="21" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="21" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="21" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="21" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="18">
+      <c r="A12" s="27" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="21"/>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="21" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="21" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="21" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="21" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="21" t="s">
+        <v>272</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{432494A1-C4B1-460B-AB55-EF2B23AA13B9}">
   <dimension ref="A1:A11"/>
@@ -1391,7 +1972,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CA2D8E8-3FB3-4A44-8F39-3D1D26FA5581}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -1410,6 +1991,11 @@
     <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -1504,7 +2090,7 @@
         <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1627,7 +2213,7 @@
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>68</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -1650,16 +2236,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="24" thickBot="1">
       <c r="A1" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>75</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>7</v>
@@ -1667,257 +2253,257 @@
     </row>
     <row r="2" spans="1:5" ht="24" thickBot="1">
       <c r="A2" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>29</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="24" thickBot="1">
       <c r="A3" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>30</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="24" thickBot="1">
       <c r="A4" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>88</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="47.25" thickBot="1">
       <c r="A5" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>32</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>95</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="24" thickBot="1">
       <c r="A6" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>33</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="24" thickBot="1">
       <c r="A7" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>34</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="24" thickBot="1">
       <c r="A8" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>35</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="24" thickBot="1">
       <c r="A9" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>36</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="24" thickBot="1">
       <c r="A10" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="24" thickBot="1">
       <c r="A11" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>38</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="24" thickBot="1">
       <c r="A12" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>39</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="24" thickBot="1">
       <c r="A13" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>40</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="24" thickBot="1">
       <c r="A14" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>41</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="24" thickBot="1">
       <c r="A15" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>42</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="24" thickBot="1">
       <c r="A16" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1927,7 +2513,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F71EF793-F7CD-4550-B042-57D9319D3DDD}">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="34.140625" style="11" bestFit="1" customWidth="1"/>
@@ -1940,941 +2526,1304 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" thickBot="1">
       <c r="A1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:5" thickBot="1">
-      <c r="A2" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>110</v>
+      <c r="C2" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:5" thickBot="1">
       <c r="A3" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>30</v>
       </c>
       <c r="C3" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" thickBot="1">
+      <c r="A4" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" hidden="1" thickBot="1">
+      <c r="A5" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" thickBot="1">
-      <c r="A4" s="10" t="s">
+      <c r="D5" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" hidden="1" thickBot="1">
+      <c r="A6" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E4" s="10" t="s">
+      <c r="B6" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="16" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:5" thickBot="1">
-      <c r="A5" s="10" t="s">
+    <row r="7" spans="1:5" hidden="1" thickBot="1">
+      <c r="A7" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" hidden="1" thickBot="1">
+      <c r="A8" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" hidden="1" thickBot="1">
+      <c r="A9" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" hidden="1" thickBot="1">
+      <c r="A10" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D10" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" s="10" t="s">
+      <c r="E10" s="16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" hidden="1" thickBot="1">
+      <c r="A11" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" s="16" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:5" thickBot="1">
-      <c r="A6" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E6" s="10" t="s">
+    <row r="12" spans="1:5" hidden="1" thickBot="1">
+      <c r="A12" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" hidden="1" thickBot="1">
+      <c r="A13" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" hidden="1" thickBot="1">
+      <c r="A14" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" hidden="1" thickBot="1">
+      <c r="A15" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" hidden="1" thickBot="1">
+      <c r="A16" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="17" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="1:5" thickBot="1">
-      <c r="A7" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" thickBot="1">
-      <c r="A8" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" thickBot="1">
-      <c r="A9" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" thickBot="1">
-      <c r="A10" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" thickBot="1">
-      <c r="A11" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" s="10" t="s">
+    <row r="17" spans="1:6" thickBot="1">
+      <c r="A17" s="14" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" thickBot="1">
-      <c r="A12" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" thickBot="1">
-      <c r="A13" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" thickBot="1">
-      <c r="A14" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" thickBot="1">
-      <c r="A15" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" thickBot="1">
-      <c r="A16" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" thickBot="1">
-      <c r="A17" s="10" t="s">
+      <c r="B17" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>198</v>
+      <c r="D17" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>185</v>
       </c>
       <c r="F17" s="12"/>
     </row>
     <row r="18" spans="1:6" thickBot="1">
       <c r="A18" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D18" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="E18" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="F18" s="12"/>
+    </row>
+    <row r="19" spans="1:6" thickBot="1">
+      <c r="A19" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="F18" s="12"/>
-    </row>
-    <row r="19" spans="1:6" thickBot="1">
-      <c r="A19" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="10" t="s">
+      <c r="D19" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F19" s="12"/>
+    </row>
+    <row r="20" spans="1:6" thickBot="1">
+      <c r="A20" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="D19" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="F19" s="12"/>
-    </row>
-    <row r="20" spans="1:6" thickBot="1">
-      <c r="A20" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="10" t="s">
+      <c r="D20" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="D20" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>200</v>
+      <c r="E20" s="14" t="s">
+        <v>187</v>
       </c>
       <c r="F20" s="12"/>
     </row>
     <row r="21" spans="1:6" thickBot="1">
       <c r="A21" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F21" s="12"/>
+    </row>
+    <row r="22" spans="1:6" thickBot="1">
+      <c r="A22" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="D22" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="E22" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="F22" s="12"/>
+    </row>
+    <row r="23" spans="1:6" thickBot="1">
+      <c r="A23" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="D23" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="E21" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="F21" s="12"/>
-    </row>
-    <row r="22" spans="1:6" thickBot="1">
-      <c r="A22" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="F22" s="12"/>
-    </row>
-    <row r="23" spans="1:6" thickBot="1">
-      <c r="A23" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="10" t="s">
+      <c r="E23" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" thickBot="1">
+      <c r="A24" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D23" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="F23" s="12"/>
-    </row>
-    <row r="24" spans="1:6" thickBot="1">
-      <c r="A24" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="F24" s="12"/>
+      <c r="D24" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="25" spans="1:6" ht="30.75" thickBot="1">
       <c r="A25" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>19</v>
       </c>
       <c r="C25" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F25" s="12"/>
+    </row>
+    <row r="26" spans="1:6" thickBot="1">
+      <c r="A26" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="D25" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="F25" s="12"/>
-    </row>
-    <row r="26" spans="1:6" thickBot="1">
-      <c r="A26" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="10" t="s">
+      <c r="D26" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="F26" s="12"/>
+    </row>
+    <row r="27" spans="1:6" thickBot="1">
+      <c r="A27" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D27" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="E26" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="F26" s="12"/>
-    </row>
-    <row r="27" spans="1:6" thickBot="1">
-      <c r="A27" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="10" t="s">
+      <c r="E27" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" thickBot="1">
+      <c r="A28" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="D27" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="F27" s="12"/>
-    </row>
-    <row r="28" spans="1:6" thickBot="1">
-      <c r="A28" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" s="10" t="s">
+      <c r="D28" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="F28" s="12"/>
+    </row>
+    <row r="29" spans="1:6" thickBot="1">
+      <c r="A29" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="D28" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="F28" s="12"/>
-    </row>
-    <row r="29" spans="1:6" thickBot="1">
-      <c r="A29" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" s="10" t="s">
+      <c r="D29" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="F29" s="12"/>
+    </row>
+    <row r="30" spans="1:6" thickBot="1">
+      <c r="A30" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="D29" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="F29" s="12"/>
-    </row>
-    <row r="30" spans="1:6" thickBot="1">
-      <c r="A30" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>214</v>
+      <c r="D30" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>201</v>
       </c>
       <c r="F30" s="12"/>
     </row>
     <row r="31" spans="1:6" thickBot="1">
       <c r="A31" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C31" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="F31" s="12"/>
+    </row>
+    <row r="32" spans="1:6" thickBot="1">
+      <c r="A32" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D31" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="F31" s="12"/>
-    </row>
-    <row r="32" spans="1:6" thickBot="1">
-      <c r="A32" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="F32" s="12"/>
+      <c r="D32" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="33" spans="1:6" thickBot="1">
       <c r="A33" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>27</v>
       </c>
       <c r="C33" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="F33" s="12"/>
+    </row>
+    <row r="34" spans="1:6" ht="30.75" thickBot="1">
+      <c r="A34" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="D33" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="F33" s="12"/>
-    </row>
-    <row r="34" spans="1:6" ht="30.75" thickBot="1">
-      <c r="A34" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>211</v>
+      <c r="D34" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>198</v>
       </c>
       <c r="F34" s="12"/>
     </row>
     <row r="35" spans="1:6" ht="16.5" thickBot="1">
       <c r="A35" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C35" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="D35" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="E35" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="E35" s="10" t="s">
+      <c r="F35" s="8"/>
+    </row>
+    <row r="36" spans="1:6" ht="30.75" thickBot="1">
+      <c r="A36" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="B36" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="F35" s="8" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="30.75" thickBot="1">
-      <c r="A36" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="B36" s="10" t="s">
+      <c r="C36" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="D36" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="F36" s="8"/>
+    </row>
+    <row r="37" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A37" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="D36" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A37" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="10" t="s">
+      <c r="D37" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="E37" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="E37" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>188</v>
-      </c>
+      <c r="F37" s="8"/>
     </row>
     <row r="38" spans="1:6" ht="16.5" thickBot="1">
       <c r="A38" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>3</v>
       </c>
       <c r="C38" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E38" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="D38" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="E38" s="10" t="s">
+      <c r="F38" s="8"/>
+    </row>
+    <row r="39" spans="1:6" ht="30.75" thickBot="1">
+      <c r="A39" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="F38" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="30.75" thickBot="1">
-      <c r="A39" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C39" s="10" t="s">
+      <c r="D39" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="E39" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="E39" s="10" t="s">
+      <c r="F39" s="8"/>
+    </row>
+    <row r="40" spans="1:6" ht="30.75" thickBot="1">
+      <c r="A40" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="F39" s="8" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="30.75" thickBot="1">
-      <c r="A40" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40" s="10" t="s">
+      <c r="D40" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="E40" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="D40" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>191</v>
-      </c>
+      <c r="F40" s="8"/>
     </row>
     <row r="41" spans="1:6" ht="16.5" thickBot="1">
       <c r="A41" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C41" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="D41" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="D41" s="10" t="s">
-        <v>154</v>
-      </c>
       <c r="E41" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F41" s="8"/>
+    </row>
+    <row r="42" spans="1:6" ht="30.75" thickBot="1">
+      <c r="A42" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="C42" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="F41" s="8" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="30.75" thickBot="1">
-      <c r="A42" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="C42" s="10" t="s">
+      <c r="D42" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="F42" s="8"/>
+    </row>
+    <row r="43" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A43" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="D42" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A43" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="10" t="s">
+      <c r="D43" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="E43" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="D43" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>193</v>
-      </c>
+      <c r="F43" s="8"/>
     </row>
     <row r="44" spans="1:6" ht="16.5" thickBot="1">
       <c r="A44" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>3</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E44" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="F44" s="8"/>
+    </row>
+    <row r="45" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A45" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="E45" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="F44" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A45" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>190</v>
-      </c>
+      <c r="F45" s="8"/>
     </row>
     <row r="46" spans="1:6" ht="30.75" thickBot="1">
       <c r="A46" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B46" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C46" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="D46" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E46" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="D46" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>194</v>
-      </c>
+      <c r="F46" s="8"/>
     </row>
     <row r="47" spans="1:6" ht="16.5" thickBot="1">
       <c r="A47" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="F47" s="8"/>
+    </row>
+    <row r="48" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A48" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="E48" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="F47" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="16.5" thickBot="1">
-      <c r="A48" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>191</v>
-      </c>
+      <c r="F48" s="8"/>
     </row>
     <row r="49" spans="1:6" ht="16.5" thickBot="1">
       <c r="A49" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C49" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E49" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="D49" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>195</v>
-      </c>
+      <c r="F49" s="8"/>
     </row>
     <row r="50" spans="1:6" ht="30.75" thickBot="1">
       <c r="A50" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C50" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E50" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="D50" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E50" s="10" t="s">
+      <c r="F50" s="8"/>
+    </row>
+    <row r="51" spans="1:6" ht="30.75" thickBot="1">
+      <c r="A51" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="F50" s="8" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="30.75" thickBot="1">
-      <c r="A51" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="10" t="s">
+      <c r="D51" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="E51" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="D51" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="F51" s="8" t="s">
-        <v>197</v>
+      <c r="F51" s="8"/>
+    </row>
+    <row r="54" spans="1:6" ht="16.5" thickBot="1"/>
+    <row r="55" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A55" s="13"/>
+    </row>
+    <row r="56" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A56" s="13"/>
+    </row>
+    <row r="57" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A57" s="13"/>
+    </row>
+    <row r="58" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A58" s="13"/>
+    </row>
+    <row r="59" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A59" s="13"/>
+    </row>
+    <row r="60" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A60" s="13"/>
+    </row>
+    <row r="61" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A61" s="13"/>
+    </row>
+    <row r="62" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A62" s="13"/>
+    </row>
+    <row r="63" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A63" s="13"/>
+    </row>
+    <row r="64" spans="1:6" ht="16.5" thickBot="1">
+      <c r="A64" s="13"/>
+    </row>
+    <row r="65" spans="1:1" ht="16.5" thickBot="1">
+      <c r="A65" s="13"/>
+    </row>
+    <row r="66" spans="1:1" ht="16.5" thickBot="1">
+      <c r="A66" s="13"/>
+    </row>
+    <row r="67" spans="1:1" ht="16.5" thickBot="1">
+      <c r="A67" s="13"/>
+    </row>
+    <row r="68" spans="1:1" ht="16.5" thickBot="1">
+      <c r="A68" s="13"/>
+    </row>
+    <row r="69" spans="1:1" ht="16.5" thickBot="1">
+      <c r="A69" s="13"/>
+    </row>
+    <row r="70" spans="1:1" ht="16.5" thickBot="1">
+      <c r="A70" s="13"/>
+    </row>
+    <row r="71" spans="1:1" ht="16.5" thickBot="1">
+      <c r="A71" s="13"/>
+    </row>
+    <row r="72" spans="1:1" ht="16.5" thickBot="1">
+      <c r="A72" s="13"/>
+    </row>
+    <row r="73" spans="1:1" ht="16.5" thickBot="1">
+      <c r="A73" s="13"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F51" xr:uid="{FDF02640-24A9-4923-AB48-FFA9B96E5DC4}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2EFD5B-095C-4E9E-AAEF-23B59F4A798C}">
+  <dimension ref="A1:D77"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="43.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1" s="18"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="B2" s="19"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="B3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="20" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="B7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="B9" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="B10" s="21"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="B11" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="B12" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="B13" s="21" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="B15" s="21"/>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20" s="21"/>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21" s="21" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22" s="21" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="B23" s="21" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="B25" t="s">
+        <v>227</v>
+      </c>
+      <c r="D25" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="B26" s="21"/>
+      <c r="D26" s="21"/>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="B27" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="B28" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4">
+      <c r="D29" s="22" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4">
+      <c r="D30" s="22" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="20" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="B35" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="20" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="B39" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="B40" s="21"/>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="B41" s="23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="B42" s="23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="B44" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="B46" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="C46" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="D46" s="24" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="B47" s="25" t="s">
+        <v>242</v>
+      </c>
+      <c r="C47" s="25"/>
+      <c r="D47" s="25"/>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="B48" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="C48" s="25"/>
+      <c r="D48" s="25"/>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="B49" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="C49" s="25"/>
+      <c r="D49" s="25"/>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="B51" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="B52" s="21"/>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="B53" s="21" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="B54" s="22" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="B55" s="22" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="B57" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="B58" s="21"/>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="B59" s="21" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="20" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="B63" t="s">
+        <v>227</v>
+      </c>
+      <c r="C63" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="B64" s="21"/>
+      <c r="C64" s="21"/>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="B65" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="C65" s="21" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="B66" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="C66" s="21" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="B67" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="C67" s="22" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="B68" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="C68" s="22" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="20" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="B73" t="s">
+        <v>238</v>
+      </c>
+      <c r="C73" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="B74" s="21"/>
+      <c r="C74" s="21"/>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="B75" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="C75" s="21" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="B76" s="21" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="B77" s="21" t="s">
+        <v>252</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>